--- a/tests/fixtures/normal/_diff_scope_commit_smoke_test2.xlsx
+++ b/tests/fixtures/normal/_diff_scope_commit_smoke_test2.xlsx
@@ -23,7 +23,7 @@
         <v>Apple</v>
       </c>
       <c r="B2">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
